--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="235">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -476,11 +476,277 @@
     <t>Adresse et code officiel géographique du lieu de naissance.</t>
   </si>
   <si>
-    <t>Patient.personnePhysique.lieuNaissance.CodeOfficielGeographiqueLieuNaissance</t>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.use</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>home | work | temp | old | billing - purpose of this address</t>
+  </si>
+  <si>
+    <t>The purpose of this address.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an address is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows an appropriate address to be chosen from a list of many.</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of an address.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.use</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.type</t>
+  </si>
+  <si>
+    <t>postal | physical | both</t>
+  </si>
+  <si>
+    <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
+  </si>
+  <si>
+    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>The type of an address (physical / postal).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/address-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Address.type</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.text</t>
+  </si>
+  <si>
+    <t>Text representation of the address</t>
+  </si>
+  <si>
+    <t>Specifies the entire address as it should be displayed e.g. on a postal label. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street, Erewhon 9132</t>
+  </si>
+  <si>
+    <t>Address.text</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.line</t>
+  </si>
+  <si>
+    <t>Street name, number, direction &amp; P.O. Box etc.</t>
+  </si>
+  <si>
+    <t>This component contains the house number, apartment number, street name, street direction,  P.O. Box number, delivery hints, and similar address information.</t>
+  </si>
+  <si>
+    <t>137 Nowhere Street</t>
+  </si>
+  <si>
+    <t>Address.line</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.city</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municpality
+</t>
+  </si>
+  <si>
+    <t>Name of city, town etc.</t>
+  </si>
+  <si>
+    <t>The name of the city, town, suburb, village or other community or delivery center.</t>
+  </si>
+  <si>
+    <t>Erewhon</t>
+  </si>
+  <si>
+    <t>Address.city</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.district</t>
+  </si>
+  <si>
+    <t xml:space="preserve">County
+</t>
+  </si>
+  <si>
+    <t>District name (aka county)</t>
+  </si>
+  <si>
+    <t>The name of the administrative area (county).</t>
+  </si>
+  <si>
+    <t>District is sometimes known as county, but in some regions 'county' is used in place of city (municipality), so county name should be conveyed in city instead.</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>Address.district</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.state</t>
+  </si>
+  <si>
+    <t>Province
+Territory</t>
+  </si>
+  <si>
+    <t>Sub-unit of country (abbreviations ok)</t>
+  </si>
+  <si>
+    <t>Sub-unit of a country with limited sovereignty in a federally organized country. A code may be used if codes are in common use (e.g. US 2 letter state codes).</t>
+  </si>
+  <si>
+    <t>Address.state</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.postalCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zip
+</t>
+  </si>
+  <si>
+    <t>Postal code for area</t>
+  </si>
+  <si>
+    <t>A postal code designating a region defined by the postal service.</t>
+  </si>
+  <si>
+    <t>9132</t>
+  </si>
+  <si>
+    <t>Address.postalCode</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.country</t>
+  </si>
+  <si>
+    <t>Country (e.g. can be ISO 3166 2 or 3 letter code)</t>
+  </si>
+  <si>
+    <t>Country - a nation as commonly understood or generally accepted.</t>
+  </si>
+  <si>
+    <t>ISO 3166 3 letter codes can be used in place of a human readable country name.</t>
+  </si>
+  <si>
+    <t>Address.country</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use</t>
+  </si>
+  <si>
+    <t>Time period when address was/is in use.</t>
+  </si>
+  <si>
+    <t>Allows addresses to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
+  &lt;start value="2010-03-23"/&gt;
+  &lt;end value="2010-07-01"/&gt;
+&lt;/valuePeriod&gt;</t>
+  </si>
+  <si>
+    <t>Address.period</t>
+  </si>
+  <si>
+    <t>Patient.personnePhysique.lieuNaissance.adresseLieuNaissance.codeOfficielGeographiqueLieuNaissance</t>
   </si>
   <si>
     <t>Code Officiel Géographique (COG) de la commune ou du pays du lieu de naissance.
-    - Le COG est obligatoire si le matricule INS est présent.</t>
+     - Le COG est obligatoire si le matricule INS est présent.</t>
   </si>
 </sst>
 </file>
@@ -782,13 +1048,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="96.12109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="96.12109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -799,21 +1065,21 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="51.3125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="34.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="37.3046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="96.12109375" customWidth="true" bestFit="true" hidden="true"/>
@@ -4129,15 +4395,15 @@
         <v>72</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>72</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4163,10 +4429,10 @@
         <v>95</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4217,18 +4483,1236 @@
         <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>72</v>
       </c>
     </row>
